--- a/checklists/excel/fo/ops.xlsx
+++ b/checklists/excel/fo/ops.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Operations" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Operational Readiness" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,94 +425,98 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Item Text</t>
+          <t>Sr.No.</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Item Type</t>
+          <t>Main Category</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Details</t>
+          <t>Sub Category</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Description</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Technical Description</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>How to Measure</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Deployment and monitoring considerations addressed (MUST)</t>
-        </is>
+      <c r="A2" t="n">
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MUST</t>
+          <t>Operational Readiness</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Logging implemented; Metrics exposed; Health checks available; Deployment process documented</t>
+          <t>Verify logging implementation</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Code should be production-ready with proper observability</t>
+          <t>Ensure proper logging is implemented for monitoring and debugging purposes.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Uses structured logging with appropriate log levels</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Check log output and log aggregation setup</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Configuration management is proper (GOOD)</t>
-        </is>
+      <c r="A3" t="n">
+        <v>2</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GOOD</t>
+          <t>Operational Readiness</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Environment-specific configs; Secrets management; Feature flags implemented</t>
+          <t>Check monitoring setup</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Configuration should be properly externalized and managed</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Backup and recovery procedures considered (GOOD)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GOOD</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Data backup strategy; Recovery procedures; Disaster recovery planning</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Operational continuity should be planned for</t>
+          <t>Verify that monitoring and alerting are properly configured for the application.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Metrics, health checks, and alerting configured</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Test monitoring endpoints and alerting rules</t>
         </is>
       </c>
     </row>
